--- a/Exc2/FURPS.xlsx
+++ b/Exc2/FURPS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\downloads\as-9\Exc2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AAB46F7-6A4B-4C50-8856-C767158CABC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8315043E-7856-47B5-A1CB-21896CB91519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="73">
   <si>
     <t>Код</t>
   </si>
@@ -190,16 +190,55 @@
     <t>Ограниченные возможности вертикального масштабирования АБС.</t>
   </si>
   <si>
-    <t>Необходимость разработки документации для дальнейшего расширения системы.</t>
-  </si>
-  <si>
     <t>Так как АБС перегружена, важно избежать прямого обращения интернет-банка к АБС, чтобы не затруднять её работу.</t>
   </si>
   <si>
     <t>Так как АБС масштабируется только вертикально, нужно учитывать эти ограничения при разработке нового функционала, чтобы не создать угрозы для её производительности.</t>
   </si>
   <si>
-    <t>Для того чтобы обеспечить дальнейшее развитие и поддержку системы, нужно предусмотреть подробную документацию для текущей и будущей разработки.</t>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>F5</t>
+  </si>
+  <si>
+    <t>F6</t>
+  </si>
+  <si>
+    <t>Сотрудник колл-центра должен обрабатывать заявки с сайта в системе колл-центра и отправлять их далее в АБС</t>
+  </si>
+  <si>
+    <t>Менеджер по депозитным процессам обрабатывает заявки в бек-офисе, подтверждая условия депозита в АБС банка</t>
+  </si>
+  <si>
+    <t>Сотрудник отделения может подать заявку напрямую в АБС, если клиент сразу придет в отделение, чтобы открыть депозит</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>Необходима документация</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>Не дорабатывать функционал подрядчика в интернет-банке</t>
+  </si>
+  <si>
+    <t>Текущая платформа интернет-банка не совместима с Kafka</t>
+  </si>
+  <si>
+    <t>Использование существующих баз данных Oracle, MS SQL</t>
+  </si>
+  <si>
+    <t>Использование платформ Java, .NET, PHP</t>
   </si>
 </sst>
 </file>
@@ -310,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -319,13 +358,9 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -334,6 +369,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="B1:D32"/>
   <sheetFormatPr defaultColWidth="10.36328125" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="10.36328125" style="1"/>
@@ -589,30 +627,30 @@
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="2:4" ht="77.5">
       <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="46.5">
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -620,212 +658,270 @@
       <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="30" customHeight="1">
+    <row r="8" spans="2:4" ht="62">
       <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="4"/>
+        <v>58</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="6"/>
     </row>
     <row r="9" spans="2:4" ht="62">
       <c r="B9" s="3" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>34</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="D9" s="6"/>
     </row>
     <row r="10" spans="2:4" ht="62">
       <c r="B10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" spans="2:4" ht="30" customHeight="1">
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="2:4" ht="62">
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="62">
+      <c r="B13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D13" s="6" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="62">
-      <c r="B11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" ht="30" customHeight="1">
-      <c r="B12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="2:4" ht="46.5">
-      <c r="B13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="62">
       <c r="B14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="30" customHeight="1">
+      <c r="B15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="8"/>
+    </row>
+    <row r="16" spans="2:4" ht="46.5">
+      <c r="B16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="62">
+      <c r="B17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D17" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="62">
-      <c r="B15" s="3" t="s">
+    <row r="18" spans="2:4" ht="62">
+      <c r="B18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="30" customHeight="1">
-      <c r="B16" s="3" t="s">
+    <row r="19" spans="2:4" ht="30" customHeight="1">
+      <c r="B19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C19" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" spans="1:4" ht="62">
-      <c r="B17" s="3" t="s">
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="2:4" ht="62">
+      <c r="B20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D20" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="62">
-      <c r="B18" s="3" t="s">
+    <row r="21" spans="2:4" ht="62">
+      <c r="B21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D21" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="30" customHeight="1">
-      <c r="B19" s="3" t="s">
+    <row r="22" spans="2:4" ht="30" customHeight="1">
+      <c r="B22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C22" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="1:4" ht="77.5">
-      <c r="B20" s="3" t="s">
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="2:4" ht="77.5">
+      <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D23" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="62">
-      <c r="B21" s="3" t="s">
+    <row r="24" spans="2:4" ht="62">
+      <c r="B24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D24" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="30" customHeight="1">
-      <c r="B22" s="3" t="s">
+    <row r="25" spans="2:4" ht="15.5">
+      <c r="B25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="6"/>
+    </row>
+    <row r="26" spans="2:4" ht="30" customHeight="1">
+      <c r="B26" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C26" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="1:4" ht="46.5">
-      <c r="A23" s="6"/>
-      <c r="B23" s="9" t="s">
+      <c r="D26" s="8"/>
+    </row>
+    <row r="27" spans="2:4" ht="46.5">
+      <c r="B27" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D27" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="77.5">
+      <c r="B28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="77.5">
-      <c r="A24" s="6"/>
-      <c r="B24" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="62">
-      <c r="A25" s="6"/>
-      <c r="B25" s="9" t="s">
+    <row r="29" spans="2:4" ht="31">
+      <c r="B29" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>59</v>
-      </c>
+      <c r="C29" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="6"/>
+    </row>
+    <row r="30" spans="2:4" ht="31">
+      <c r="B30" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" s="6"/>
+    </row>
+    <row r="31" spans="2:4" ht="31">
+      <c r="B31" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="6"/>
+    </row>
+    <row r="32" spans="2:4" ht="31">
+      <c r="B32" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C19:D19"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C19:D19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
